--- a/Data_Structuring/Methodology_for_Real_World_Data_Collection/Step-01- Source-Identity-Collection/Top 500 Actor_Actress_List.xlsx
+++ b/Data_Structuring/Methodology_for_Real_World_Data_Collection/Step-01- Source-Identity-Collection/Top 500 Actor_Actress_List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real-vs-Fake\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amna Amjid\Downloads\SGFF-Net-Github-Rep\Data_Structuring\Methodology_for_Real_World_Data_Collection\Step-01- Source-Identity-Collection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E209D82-087B-4DEE-9516-36457344888E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B249B5AB-B147-44E7-9278-4B6A4D09005D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1528,7 +1528,7 @@
     <t>keiko kitagawa</t>
   </si>
   <si>
-    <t>Identity_Name</t>
+    <t>Name</t>
   </si>
 </sst>
 </file>
